--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/31.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/31.xlsx
@@ -426,13 +426,13 @@
         <v>-13.34458287255865</v>
       </c>
       <c r="E2">
-        <v>-12.3652313068259</v>
+        <v>-13.32410850710606</v>
       </c>
       <c r="F2">
-        <v>-1.829885277584088</v>
+        <v>-1.003267386739295</v>
       </c>
       <c r="G2">
-        <v>-8.850903556095737</v>
+        <v>-8.774953020333777</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.37755428892693</v>
       </c>
       <c r="E3">
-        <v>-13.32955173286328</v>
+        <v>-14.5111030570486</v>
       </c>
       <c r="F3">
-        <v>-1.986767294898078</v>
+        <v>-1.183275765204642</v>
       </c>
       <c r="G3">
-        <v>-8.535484708750596</v>
+        <v>-8.892772025530901</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.36874456353052</v>
       </c>
       <c r="E4">
-        <v>-14.28356535205919</v>
+        <v>-15.16943449438768</v>
       </c>
       <c r="F4">
-        <v>-1.789301901786135</v>
+        <v>-1.025244802302969</v>
       </c>
       <c r="G4">
-        <v>-8.610173926662094</v>
+        <v>-9.350865453982012</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.27321584540769</v>
       </c>
       <c r="E5">
-        <v>-15.66851761477303</v>
+        <v>-16.14375379103399</v>
       </c>
       <c r="F5">
-        <v>-1.904553486905033</v>
+        <v>-0.9896291458196044</v>
       </c>
       <c r="G5">
-        <v>-8.058792635459859</v>
+        <v>-8.479715258596034</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.08117590408669</v>
       </c>
       <c r="E6">
-        <v>-15.9698332182954</v>
+        <v>-16.92613371686519</v>
       </c>
       <c r="F6">
-        <v>-1.795494776489464</v>
+        <v>-1.266627750009134</v>
       </c>
       <c r="G6">
-        <v>-7.845891451829329</v>
+        <v>-8.882760935820144</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.75896399934252</v>
       </c>
       <c r="E7">
-        <v>-15.80601567106793</v>
+        <v>-17.09534014816179</v>
       </c>
       <c r="F7">
-        <v>-1.863672727209475</v>
+        <v>-0.838937518106735</v>
       </c>
       <c r="G7">
-        <v>-7.512036176375988</v>
+        <v>-8.431334946085125</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.30461777619339</v>
       </c>
       <c r="E8">
-        <v>-17.19289706370903</v>
+        <v>-18.1452894892102</v>
       </c>
       <c r="F8">
-        <v>-1.89632365675822</v>
+        <v>-0.9734618992191664</v>
       </c>
       <c r="G8">
-        <v>-7.11184087886119</v>
+        <v>-7.850784438136373</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.70372990054581</v>
       </c>
       <c r="E9">
-        <v>-17.64211715679593</v>
+        <v>-17.58608181942501</v>
       </c>
       <c r="F9">
-        <v>-1.976046563971047</v>
+        <v>-0.8177420813713041</v>
       </c>
       <c r="G9">
-        <v>-7.124440815183656</v>
+        <v>-8.14182442813032</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.98333247643507</v>
       </c>
       <c r="E10">
-        <v>-18.79880263020513</v>
+        <v>-18.74501794441603</v>
       </c>
       <c r="F10">
-        <v>-1.870588766655448</v>
+        <v>-1.320983562246032</v>
       </c>
       <c r="G10">
-        <v>-6.575962872419363</v>
+        <v>-7.432629431071029</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.16589484202056</v>
       </c>
       <c r="E11">
-        <v>-18.57896785950277</v>
+        <v>-20.30862303520647</v>
       </c>
       <c r="F11">
-        <v>-1.791726533174129</v>
+        <v>-0.6033357465047081</v>
       </c>
       <c r="G11">
-        <v>-5.706097168702623</v>
+        <v>-6.902899107695629</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.31547732635479</v>
       </c>
       <c r="E12">
-        <v>-20.87803335693094</v>
+        <v>-20.93677672175844</v>
       </c>
       <c r="F12">
-        <v>-1.524587157812719</v>
+        <v>-0.9454879320266271</v>
       </c>
       <c r="G12">
-        <v>-5.417771826050878</v>
+        <v>-5.928850535858024</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.483959175413183</v>
       </c>
       <c r="E13">
-        <v>-21.00213618711115</v>
+        <v>-21.35981317813298</v>
       </c>
       <c r="F13">
-        <v>-1.265864823631155</v>
+        <v>-0.7963586052354377</v>
       </c>
       <c r="G13">
-        <v>-5.014262672451269</v>
+        <v>-4.978323390076942</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.74963839655894</v>
       </c>
       <c r="E14">
-        <v>-21.32732590560196</v>
+        <v>-22.49340796257707</v>
       </c>
       <c r="F14">
-        <v>-1.72788674254258</v>
+        <v>-0.3191361444826425</v>
       </c>
       <c r="G14">
-        <v>-4.973715110686276</v>
+        <v>-4.974579163072026</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.165209118581633</v>
       </c>
       <c r="E15">
-        <v>-23.73049196351845</v>
+        <v>-22.96810977890513</v>
       </c>
       <c r="F15">
-        <v>-0.9665326058947485</v>
+        <v>-0.03434011793056126</v>
       </c>
       <c r="G15">
-        <v>-4.243382280358738</v>
+        <v>-4.72981397862601</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.787558500483232</v>
       </c>
       <c r="E16">
-        <v>-24.18975621195436</v>
+        <v>-23.97101280348785</v>
       </c>
       <c r="F16">
-        <v>-0.8988657578622653</v>
+        <v>0.1084198919005027</v>
       </c>
       <c r="G16">
-        <v>-3.347641352707055</v>
+        <v>-4.478980564206512</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.640233301452589</v>
       </c>
       <c r="E17">
-        <v>-23.83993612333583</v>
+        <v>-25.12499024944046</v>
       </c>
       <c r="F17">
-        <v>-0.4404720881751029</v>
+        <v>0.4801804135006845</v>
       </c>
       <c r="G17">
-        <v>-3.554169736174488</v>
+        <v>-3.837261106328645</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.733880102678969</v>
       </c>
       <c r="E18">
-        <v>-24.63342439590784</v>
+        <v>-25.70048684023124</v>
       </c>
       <c r="F18">
-        <v>-0.06638965274487413</v>
+        <v>0.5674895093883495</v>
       </c>
       <c r="G18">
-        <v>-3.374764652310303</v>
+        <v>-3.859650325810736</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.049817316737386</v>
       </c>
       <c r="E19">
-        <v>-25.97489425120004</v>
+        <v>-26.81347706794043</v>
       </c>
       <c r="F19">
-        <v>0.4327936562235388</v>
+        <v>0.8453429887375681</v>
       </c>
       <c r="G19">
-        <v>-3.208658029877371</v>
+        <v>-2.844173587094692</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.554251237837393</v>
       </c>
       <c r="E20">
-        <v>-26.46886472443073</v>
+        <v>-27.22581274023485</v>
       </c>
       <c r="F20">
-        <v>0.2452487911275223</v>
+        <v>1.124933554530457</v>
       </c>
       <c r="G20">
-        <v>-2.928552771799636</v>
+        <v>-3.556242137682071</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.19952284113708</v>
       </c>
       <c r="E21">
-        <v>-27.52077942319847</v>
+        <v>-27.52591018424916</v>
       </c>
       <c r="F21">
-        <v>0.5015614045343425</v>
+        <v>1.481393301833529</v>
       </c>
       <c r="G21">
-        <v>-3.256190842730228</v>
+        <v>-3.234741818181289</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.925314409087974</v>
       </c>
       <c r="E22">
-        <v>-27.5222149494589</v>
+        <v>-27.7161559057854</v>
       </c>
       <c r="F22">
-        <v>0.923683350755123</v>
+        <v>1.502052784859349</v>
       </c>
       <c r="G22">
-        <v>-3.178604897471868</v>
+        <v>-3.256031936544342</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.670248061905927</v>
       </c>
       <c r="E23">
-        <v>-28.50734371356151</v>
+        <v>-28.38736179472829</v>
       </c>
       <c r="F23">
-        <v>0.8820661724384758</v>
+        <v>1.59248234075336</v>
       </c>
       <c r="G23">
-        <v>-3.504091113801932</v>
+        <v>-3.49288160660596</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.36396683127156</v>
       </c>
       <c r="E24">
-        <v>-28.09090524381615</v>
+        <v>-29.37258565678507</v>
       </c>
       <c r="F24">
-        <v>1.163283651810463</v>
+        <v>1.855321660926837</v>
       </c>
       <c r="G24">
-        <v>-3.669999103502508</v>
+        <v>-3.93835523546137</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.95119345889517</v>
       </c>
       <c r="E25">
-        <v>-28.50281523955384</v>
+        <v>-28.66909174816749</v>
       </c>
       <c r="F25">
-        <v>1.069065143416047</v>
+        <v>1.529733509991297</v>
       </c>
       <c r="G25">
-        <v>-3.659349078502673</v>
+        <v>-3.371278647857451</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.37645976629687</v>
       </c>
       <c r="E26">
-        <v>-28.37103664593064</v>
+        <v>-29.01119531707694</v>
       </c>
       <c r="F26">
-        <v>0.6460634710134938</v>
+        <v>1.584127427128724</v>
       </c>
       <c r="G26">
-        <v>-3.711659008568696</v>
+        <v>-3.167690028828891</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.61113484900012</v>
       </c>
       <c r="E27">
-        <v>-28.95443995233881</v>
+        <v>-29.33537065739003</v>
       </c>
       <c r="F27">
-        <v>1.052378510454054</v>
+        <v>1.389676462995568</v>
       </c>
       <c r="G27">
-        <v>-3.656319929334239</v>
+        <v>-3.691487854597917</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.63148046265293</v>
       </c>
       <c r="E28">
-        <v>-28.89189719781887</v>
+        <v>-28.7561244901209</v>
       </c>
       <c r="F28">
-        <v>1.11427909299565</v>
+        <v>1.566700233708628</v>
       </c>
       <c r="G28">
-        <v>-3.946091980386647</v>
+        <v>-3.84178331153529</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.44438815005491</v>
       </c>
       <c r="E29">
-        <v>-27.83299053518329</v>
+        <v>-28.83542259846921</v>
       </c>
       <c r="F29">
-        <v>0.9265113970682805</v>
+        <v>1.530671221891266</v>
       </c>
       <c r="G29">
-        <v>-3.662259048031692</v>
+        <v>-3.923692829267937</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.06191409351375</v>
       </c>
       <c r="E30">
-        <v>-27.83298600670928</v>
+        <v>-28.56594669569478</v>
       </c>
       <c r="F30">
-        <v>1.215757413308201</v>
+        <v>1.245643252466401</v>
       </c>
       <c r="G30">
-        <v>-3.948674205907278</v>
+        <v>-3.575800840728085</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.52366380016381</v>
       </c>
       <c r="E31">
-        <v>-27.6924855721473</v>
+        <v>-28.03822550568492</v>
       </c>
       <c r="F31">
-        <v>0.7568667231793585</v>
+        <v>1.333176835920225</v>
       </c>
       <c r="G31">
-        <v>-3.738222825975809</v>
+        <v>-3.551392188467039</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.866846213596469</v>
       </c>
       <c r="E32">
-        <v>-27.12701502280951</v>
+        <v>-28.02082710854745</v>
       </c>
       <c r="F32">
-        <v>0.5980653785930821</v>
+        <v>1.437226408651065</v>
       </c>
       <c r="G32">
-        <v>-3.423641546652103</v>
+        <v>-3.714118743904375</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.148278027959698</v>
       </c>
       <c r="E33">
-        <v>-27.71550380552829</v>
+        <v>-27.99038670626789</v>
       </c>
       <c r="F33">
-        <v>0.7268864501372388</v>
+        <v>1.456330217694427</v>
       </c>
       <c r="G33">
-        <v>-3.514360426064751</v>
+        <v>-3.725023680910734</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.411096976365224</v>
       </c>
       <c r="E34">
-        <v>-27.22553197484637</v>
+        <v>-27.94754734215533</v>
       </c>
       <c r="F34">
-        <v>0.6788378273052563</v>
+        <v>1.192690694609846</v>
       </c>
       <c r="G34">
-        <v>-3.521673421161001</v>
+        <v>-3.564117925519998</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.709458228596774</v>
       </c>
       <c r="E35">
-        <v>-26.42028325527644</v>
+        <v>-26.6683394759946</v>
       </c>
       <c r="F35">
-        <v>0.9747919627730469</v>
+        <v>1.033051042211936</v>
       </c>
       <c r="G35">
-        <v>-3.678454236809806</v>
+        <v>-2.951200213833791</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.072359243464883</v>
       </c>
       <c r="E36">
-        <v>-25.24708243716126</v>
+        <v>-27.55408634952488</v>
       </c>
       <c r="F36">
-        <v>0.7241511809731949</v>
+        <v>1.19777852719784</v>
       </c>
       <c r="G36">
-        <v>-3.746863349833306</v>
+        <v>-3.07879857055392</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.537440646104542</v>
       </c>
       <c r="E37">
-        <v>-25.88200166388069</v>
+        <v>-26.11307610707009</v>
       </c>
       <c r="F37">
-        <v>0.5770165628879467</v>
+        <v>1.032267406648888</v>
       </c>
       <c r="G37">
-        <v>-3.181567835729516</v>
+        <v>-3.080827934969493</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.112452376469037</v>
       </c>
       <c r="E38">
-        <v>-25.68464623815241</v>
+        <v>-25.76444700711558</v>
       </c>
       <c r="F38">
-        <v>0.6113788994908758</v>
+        <v>1.274591379724633</v>
       </c>
       <c r="G38">
-        <v>-3.736567553206173</v>
+        <v>-2.835016618133068</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.814175004080221</v>
       </c>
       <c r="E39">
-        <v>-24.50282773400064</v>
+        <v>-25.50099397477134</v>
       </c>
       <c r="F39">
-        <v>0.7437321296405696</v>
+        <v>1.043607756393213</v>
       </c>
       <c r="G39">
-        <v>-2.979343161463135</v>
+        <v>-2.920941827604852</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.630442644795238</v>
       </c>
       <c r="E40">
-        <v>-23.72751675609542</v>
+        <v>-24.37313676689497</v>
       </c>
       <c r="F40">
-        <v>0.570520505715193</v>
+        <v>1.416863481155448</v>
       </c>
       <c r="G40">
-        <v>-2.932995523913339</v>
+        <v>-2.3672828810716</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.563509002244284</v>
       </c>
       <c r="E41">
-        <v>-23.91957839570873</v>
+        <v>-25.20657976563666</v>
       </c>
       <c r="F41">
-        <v>0.9507262329869156</v>
+        <v>1.186814256254386</v>
       </c>
       <c r="G41">
-        <v>-3.329800822795922</v>
+        <v>-2.540268817135137</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.590788609245388</v>
       </c>
       <c r="E42">
-        <v>-23.44460487094022</v>
+        <v>-23.87598730491089</v>
       </c>
       <c r="F42">
-        <v>0.6580491189645999</v>
+        <v>1.378119080991709</v>
       </c>
       <c r="G42">
-        <v>-3.020446894878726</v>
+        <v>-3.093020674190629</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.705346584190027</v>
       </c>
       <c r="E43">
-        <v>-22.30271845058808</v>
+        <v>-23.30419047738438</v>
       </c>
       <c r="F43">
-        <v>0.5891753396262378</v>
+        <v>1.236809542482947</v>
       </c>
       <c r="G43">
-        <v>-3.547833352012323</v>
+        <v>-3.18359057905401</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.877844635271376</v>
       </c>
       <c r="E44">
-        <v>-22.582510217152</v>
+        <v>-23.13266093892184</v>
       </c>
       <c r="F44">
-        <v>0.8620428755780062</v>
+        <v>1.377506089113638</v>
       </c>
       <c r="G44">
-        <v>-4.023449498002797</v>
+        <v>-2.474054595804174</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.093980721908111</v>
       </c>
       <c r="E45">
-        <v>-21.19584166278925</v>
+        <v>-22.6195893623268</v>
       </c>
       <c r="F45">
-        <v>1.024732576753024</v>
+        <v>1.257778834917414</v>
       </c>
       <c r="G45">
-        <v>-4.210091434415827</v>
+        <v>-2.666476744728772</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.324080455412039</v>
       </c>
       <c r="E46">
-        <v>-21.22685265279377</v>
+        <v>-21.93773250251787</v>
       </c>
       <c r="F46">
-        <v>1.009992607187609</v>
+        <v>1.330865690866414</v>
       </c>
       <c r="G46">
-        <v>-4.152696506401482</v>
+        <v>-3.226511801970661</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.554626073771415</v>
       </c>
       <c r="E47">
-        <v>-20.6232568807854</v>
+        <v>-21.17549522907278</v>
       </c>
       <c r="F47">
-        <v>0.8755618315916941</v>
+        <v>1.328342483757487</v>
       </c>
       <c r="G47">
-        <v>-3.921325789207359</v>
+        <v>-3.598564151856114</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.764326627029397</v>
       </c>
       <c r="E48">
-        <v>-20.21027363670789</v>
+        <v>-21.33509676699912</v>
       </c>
       <c r="F48">
-        <v>0.9888659249466105</v>
+        <v>1.801809126705989</v>
       </c>
       <c r="G48">
-        <v>-4.042369265759731</v>
+        <v>-4.00385106841031</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.946982482772248</v>
       </c>
       <c r="E49">
-        <v>-20.51263531772603</v>
+        <v>-20.15516663650855</v>
       </c>
       <c r="F49">
-        <v>0.7328854868683129</v>
+        <v>1.413286590710159</v>
       </c>
       <c r="G49">
-        <v>-4.26290787794936</v>
+        <v>-3.772086396297014</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.094671956645299</v>
       </c>
       <c r="E50">
-        <v>-19.59499893023373</v>
+        <v>-20.25060875469421</v>
       </c>
       <c r="F50">
-        <v>0.8953432451705463</v>
+        <v>1.341912798550149</v>
       </c>
       <c r="G50">
-        <v>-4.533968725613806</v>
+        <v>-4.530668111711153</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.209522799913538</v>
       </c>
       <c r="E51">
-        <v>-18.7647213348234</v>
+        <v>-20.42891289027222</v>
       </c>
       <c r="F51">
-        <v>1.144421726048718</v>
+        <v>1.736016874106041</v>
       </c>
       <c r="G51">
-        <v>-4.561171478309998</v>
+        <v>-3.967448309660485</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.294365609919025</v>
       </c>
       <c r="E52">
-        <v>-18.40469859426559</v>
+        <v>-19.30761291275895</v>
       </c>
       <c r="F52">
-        <v>0.9807214166422857</v>
+        <v>1.868406552421458</v>
       </c>
       <c r="G52">
-        <v>-4.903286564883821</v>
+        <v>-4.723110123908986</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.35498672732378</v>
       </c>
       <c r="E53">
-        <v>-18.08718011074378</v>
+        <v>-19.14384970721957</v>
       </c>
       <c r="F53">
-        <v>1.170407611474539</v>
+        <v>1.862096049546932</v>
       </c>
       <c r="G53">
-        <v>-4.530237740791048</v>
+        <v>-4.033765157903165</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.39889079876512</v>
       </c>
       <c r="E54">
-        <v>-17.80773703667845</v>
+        <v>-18.09657216583568</v>
       </c>
       <c r="F54">
-        <v>0.8613006583850978</v>
+        <v>1.796520829206517</v>
       </c>
       <c r="G54">
-        <v>-5.481619007321262</v>
+        <v>-4.516164611703606</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.431134399959315</v>
       </c>
       <c r="E55">
-        <v>-16.60822125610471</v>
+        <v>-17.91010319162184</v>
       </c>
       <c r="F55">
-        <v>1.132801388122247</v>
+        <v>1.745205125337894</v>
       </c>
       <c r="G55">
-        <v>-5.384653128476009</v>
+        <v>-4.491994318721386</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.460845297320075</v>
       </c>
       <c r="E56">
-        <v>-16.80462117381737</v>
+        <v>-17.71618940613939</v>
       </c>
       <c r="F56">
-        <v>1.264631090073371</v>
+        <v>1.898560782618166</v>
       </c>
       <c r="G56">
-        <v>-5.623019028394613</v>
+        <v>-5.210088062190239</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.490563127634653</v>
       </c>
       <c r="E57">
-        <v>-16.49605095493471</v>
+        <v>-16.65430300760676</v>
       </c>
       <c r="F57">
-        <v>1.26522254439897</v>
+        <v>1.980864054290714</v>
       </c>
       <c r="G57">
-        <v>-5.761615017396201</v>
+        <v>-5.062765475147132</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.530639210631721</v>
       </c>
       <c r="E58">
-        <v>-16.32732907035693</v>
+        <v>-17.22169815839782</v>
       </c>
       <c r="F58">
-        <v>1.513091608869055</v>
+        <v>2.046826950575638</v>
       </c>
       <c r="G58">
-        <v>-5.482502922980247</v>
+        <v>-5.359880316205643</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.579641272698986</v>
       </c>
       <c r="E59">
-        <v>-15.62745341247148</v>
+        <v>-16.61596947513183</v>
       </c>
       <c r="F59">
-        <v>1.236889065753616</v>
+        <v>2.072140201670385</v>
       </c>
       <c r="G59">
-        <v>-5.867072445549685</v>
+        <v>-5.579074846906327</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.646131449851985</v>
       </c>
       <c r="E60">
-        <v>-15.89155401659881</v>
+        <v>-16.36719775552046</v>
       </c>
       <c r="F60">
-        <v>1.617904936345277</v>
+        <v>2.014268798176007</v>
       </c>
       <c r="G60">
-        <v>-5.849334542550269</v>
+        <v>-5.835996354572546</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.722629904200353</v>
       </c>
       <c r="E61">
-        <v>-15.791302659017</v>
+        <v>-16.2592389351776</v>
       </c>
       <c r="F61">
-        <v>1.694348337010421</v>
+        <v>2.034184407274112</v>
       </c>
       <c r="G61">
-        <v>-6.489663571301642</v>
+        <v>-6.25196971212751</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.814353154995827</v>
       </c>
       <c r="E62">
-        <v>-14.17095578891045</v>
+        <v>-15.54685110360895</v>
       </c>
       <c r="F62">
-        <v>1.302131282398105</v>
+        <v>2.136191225989649</v>
       </c>
       <c r="G62">
-        <v>-7.16721306355104</v>
+        <v>-5.876530674155382</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.909619366272874</v>
       </c>
       <c r="E63">
-        <v>-14.26618959729176</v>
+        <v>-15.88980602563185</v>
       </c>
       <c r="F63">
-        <v>1.209798138212461</v>
+        <v>1.816090180730253</v>
       </c>
       <c r="G63">
-        <v>-6.976221070299407</v>
+        <v>-6.433751767688891</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.010625231469541</v>
       </c>
       <c r="E64">
-        <v>-13.95353016638017</v>
+        <v>-14.94098656612274</v>
       </c>
       <c r="F64">
-        <v>1.213234206199273</v>
+        <v>1.669114609186342</v>
       </c>
       <c r="G64">
-        <v>-6.963803213981601</v>
+        <v>-7.223201009711194</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.102399868578226</v>
       </c>
       <c r="E65">
-        <v>-14.06196447649384</v>
+        <v>-14.89791172136177</v>
       </c>
       <c r="F65">
-        <v>1.319800359099819</v>
+        <v>1.939013276366477</v>
       </c>
       <c r="G65">
-        <v>-7.046709205921569</v>
+        <v>-6.360290762172463</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.18458960506864</v>
       </c>
       <c r="E66">
-        <v>-13.97643065943696</v>
+        <v>-15.70030297383287</v>
       </c>
       <c r="F66">
-        <v>1.474022488683419</v>
+        <v>1.908695029424015</v>
       </c>
       <c r="G66">
-        <v>-7.105259514329119</v>
+        <v>-7.120236422348782</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.240869891972231</v>
       </c>
       <c r="E67">
-        <v>-14.22451405099917</v>
+        <v>-15.01783024155889</v>
       </c>
       <c r="F67">
-        <v>1.153851860562188</v>
+        <v>1.866842594764973</v>
       </c>
       <c r="G67">
-        <v>-7.108950772605406</v>
+        <v>-6.912635422126625</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.270769823177925</v>
       </c>
       <c r="E68">
-        <v>-13.81246820104124</v>
+        <v>-15.65730511313004</v>
       </c>
       <c r="F68">
-        <v>1.08208542225325</v>
+        <v>1.838084992009385</v>
       </c>
       <c r="G68">
-        <v>-7.068065535195407</v>
+        <v>-7.274855451760443</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.259946293309413</v>
       </c>
       <c r="E69">
-        <v>-13.53359118622688</v>
+        <v>-14.49631758941355</v>
       </c>
       <c r="F69">
-        <v>1.122660514377176</v>
+        <v>2.165240414071022</v>
       </c>
       <c r="G69">
-        <v>-7.186195731673221</v>
+        <v>-7.472180518628702</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.212145018200182</v>
       </c>
       <c r="E70">
-        <v>-14.03489325887599</v>
+        <v>-14.64102497632866</v>
       </c>
       <c r="F70">
-        <v>1.345990022906728</v>
+        <v>1.77317246559121</v>
       </c>
       <c r="G70">
-        <v>-7.391648187840391</v>
+        <v>-7.5962862498049</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.118941107583463</v>
       </c>
       <c r="E71">
-        <v>-13.48433497444545</v>
+        <v>-14.43661418809643</v>
       </c>
       <c r="F71">
-        <v>1.062898776469608</v>
+        <v>1.585310335779922</v>
       </c>
       <c r="G71">
-        <v>-7.649046414064265</v>
+        <v>-6.825693875174285</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.990417024223195</v>
       </c>
       <c r="E72">
-        <v>-13.5536160982888</v>
+        <v>-14.1035041685662</v>
       </c>
       <c r="F72">
-        <v>1.099921829170329</v>
+        <v>1.530194082267254</v>
       </c>
       <c r="G72">
-        <v>-7.116071756060379</v>
+        <v>-7.243329126589964</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.824306243095712</v>
       </c>
       <c r="E73">
-        <v>-13.63642830246707</v>
+        <v>-15.10348179893997</v>
       </c>
       <c r="F73">
-        <v>1.067366990240308</v>
+        <v>1.766898410882407</v>
       </c>
       <c r="G73">
-        <v>-7.512807533486638</v>
+        <v>-7.5408677174775</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.636302143477466</v>
       </c>
       <c r="E74">
-        <v>-13.80793067008556</v>
+        <v>-14.59255219055055</v>
       </c>
       <c r="F74">
-        <v>1.104631926222647</v>
+        <v>1.648315960436852</v>
       </c>
       <c r="G74">
-        <v>-6.767772570419196</v>
+        <v>-7.10066778766615</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.428506759528387</v>
       </c>
       <c r="E75">
-        <v>-13.80242404569223</v>
+        <v>-14.60560778111467</v>
       </c>
       <c r="F75">
-        <v>1.211733204465401</v>
+        <v>1.470314716188489</v>
       </c>
       <c r="G75">
-        <v>-6.585748845033449</v>
+        <v>-6.978207397622969</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.219263163750471</v>
       </c>
       <c r="E76">
-        <v>-13.82511170047066</v>
+        <v>-14.64694369185668</v>
       </c>
       <c r="F76">
-        <v>0.7800775778058007</v>
+        <v>1.176580605360201</v>
       </c>
       <c r="G76">
-        <v>-6.464308103016364</v>
+        <v>-6.851029480186328</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.010957851274217</v>
       </c>
       <c r="E77">
-        <v>-14.18459102414755</v>
+        <v>-14.90391194942194</v>
       </c>
       <c r="F77">
-        <v>0.828899895791998</v>
+        <v>1.082496292485039</v>
       </c>
       <c r="G77">
-        <v>-5.808873054969297</v>
+        <v>-6.587748414539169</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.819978902276717</v>
       </c>
       <c r="E78">
-        <v>-14.8887777892883</v>
+        <v>-15.56729716375358</v>
       </c>
       <c r="F78">
-        <v>0.6825016963278385</v>
+        <v>1.181678378357029</v>
       </c>
       <c r="G78">
-        <v>-6.193482304085206</v>
+        <v>-6.387437235594487</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.645850501365982</v>
       </c>
       <c r="E79">
-        <v>-14.38897917000974</v>
+        <v>-15.70838629993656</v>
       </c>
       <c r="F79">
-        <v>0.732236046824518</v>
+        <v>0.9766160277940114</v>
       </c>
       <c r="G79">
-        <v>-5.795481898262945</v>
+        <v>-6.326797972951656</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.500843123276417</v>
       </c>
       <c r="E80">
-        <v>-14.17370457263311</v>
+        <v>-16.15872945457735</v>
       </c>
       <c r="F80">
-        <v>0.4500386088150188</v>
+        <v>1.288294233301742</v>
       </c>
       <c r="G80">
-        <v>-6.150345895708503</v>
+        <v>-6.000609920967267</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.380879525255338</v>
       </c>
       <c r="E81">
-        <v>-15.20243801295558</v>
+        <v>-16.47185531831173</v>
       </c>
       <c r="F81">
-        <v>0.2555271738614586</v>
+        <v>1.13644786142937</v>
       </c>
       <c r="G81">
-        <v>-6.338666278709944</v>
+        <v>-6.006029284015053</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.293540268411316</v>
       </c>
       <c r="E82">
-        <v>-17.123212905679</v>
+        <v>-17.3359243867673</v>
       </c>
       <c r="F82">
-        <v>0.47492690743213</v>
+        <v>0.7691249040059857</v>
       </c>
       <c r="G82">
-        <v>-5.622757495297011</v>
+        <v>-6.055078326724895</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.234443274358981</v>
       </c>
       <c r="E83">
-        <v>-16.26193337721216</v>
+        <v>-18.39689603355038</v>
       </c>
       <c r="F83">
-        <v>0.07808424924258205</v>
+        <v>0.7736908651302165</v>
       </c>
       <c r="G83">
-        <v>-5.918375969771771</v>
+        <v>-5.966534475731549</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.207279502627407</v>
       </c>
       <c r="E84">
-        <v>-17.15561866567789</v>
+        <v>-18.86325187228229</v>
       </c>
       <c r="F84">
-        <v>0.2964145604962393</v>
+        <v>0.6807463858013064</v>
       </c>
       <c r="G84">
-        <v>-4.720541140570512</v>
+        <v>-5.682377109913745</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.208578219456335</v>
       </c>
       <c r="E85">
-        <v>-18.38531219703875</v>
+        <v>-20.39579163138012</v>
       </c>
       <c r="F85">
-        <v>-0.1884678136302429</v>
+        <v>0.4975579048766125</v>
       </c>
       <c r="G85">
-        <v>-5.372930486721449</v>
+        <v>-5.569441159387048</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.23899096030251</v>
       </c>
       <c r="E86">
-        <v>-19.69491065226496</v>
+        <v>-20.86632725162112</v>
       </c>
       <c r="F86">
-        <v>-0.2056522954013186</v>
+        <v>0.317470831508</v>
       </c>
       <c r="G86">
-        <v>-5.067019526165096</v>
+        <v>-4.786980478998146</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.297506648720449</v>
       </c>
       <c r="E87">
-        <v>-20.71874881218514</v>
+        <v>-22.23750389640362</v>
       </c>
       <c r="F87">
-        <v>-0.5250218922440428</v>
+        <v>0.2746839984185999</v>
       </c>
       <c r="G87">
-        <v>-4.661123469231673</v>
+        <v>-5.68757797695594</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.383223173433123</v>
       </c>
       <c r="E88">
-        <v>-22.35521704975901</v>
+        <v>-23.19065257706407</v>
       </c>
       <c r="F88">
-        <v>-0.5169030633292049</v>
+        <v>0.1157037264733188</v>
       </c>
       <c r="G88">
-        <v>-4.105458332101622</v>
+        <v>-5.223005810884475</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.498861291373922</v>
       </c>
       <c r="E89">
-        <v>-23.89368005285886</v>
+        <v>-24.91317540620569</v>
       </c>
       <c r="F89">
-        <v>-0.61607769389457</v>
+        <v>0.04004147626901475</v>
       </c>
       <c r="G89">
-        <v>-3.961284073866362</v>
+        <v>-4.554576871595769</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.641988097483169</v>
       </c>
       <c r="E90">
-        <v>-25.39943841667532</v>
+        <v>-26.65583183078541</v>
       </c>
       <c r="F90">
-        <v>-0.8963061025876148</v>
+        <v>-0.06707885442400331</v>
       </c>
       <c r="G90">
-        <v>-4.012994795189778</v>
+        <v>-4.492255851818989</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.819398077012541</v>
       </c>
       <c r="E91">
-        <v>-26.9415740121954</v>
+        <v>-27.88369133017317</v>
       </c>
       <c r="F91">
-        <v>-1.367077238007407</v>
+        <v>-0.626613698890777</v>
       </c>
       <c r="G91">
-        <v>-4.695963650486963</v>
+        <v>-4.957053134987125</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.027124164459951</v>
       </c>
       <c r="E92">
-        <v>-28.46900565261258</v>
+        <v>-29.35187241667398</v>
       </c>
       <c r="F92">
-        <v>-1.371617519742152</v>
+        <v>-0.7972466150912387</v>
       </c>
       <c r="G92">
-        <v>-4.10442213134783</v>
+        <v>-5.117952269286783</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.274859535072192</v>
       </c>
       <c r="E93">
-        <v>-30.30330027721152</v>
+        <v>-31.40793547037655</v>
       </c>
       <c r="F93">
-        <v>-1.407344177457492</v>
+        <v>-0.7451530742313862</v>
       </c>
       <c r="G93">
-        <v>-3.87439549564265</v>
+        <v>-4.366862318428014</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.55556327134347</v>
       </c>
       <c r="E94">
-        <v>-32.19196602498355</v>
+        <v>-33.33682991699573</v>
       </c>
       <c r="F94">
-        <v>-1.9346364775051</v>
+        <v>-1.22196963495681</v>
       </c>
       <c r="G94">
-        <v>-4.332690867371657</v>
+        <v>-4.244027836738896</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.878528169121889</v>
       </c>
       <c r="E95">
-        <v>-34.53467016218664</v>
+        <v>-35.99071267410989</v>
       </c>
       <c r="F95">
-        <v>-2.186100656503335</v>
+        <v>-1.481159996720955</v>
       </c>
       <c r="G95">
-        <v>-4.392585257268151</v>
+        <v>-4.855452492386892</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.237520410026049</v>
       </c>
       <c r="E96">
-        <v>-36.35396195239817</v>
+        <v>-38.410767675838</v>
       </c>
       <c r="F96">
-        <v>-2.521751814648083</v>
+        <v>-1.443018648026455</v>
       </c>
       <c r="G96">
-        <v>-4.330191405489507</v>
+        <v>-4.764826308249343</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.634512175131768</v>
       </c>
       <c r="E97">
-        <v>-38.60404973919638</v>
+        <v>-40.70321707274096</v>
       </c>
       <c r="F97">
-        <v>-2.743343408366562</v>
+        <v>-1.982973372193257</v>
       </c>
       <c r="G97">
-        <v>-4.191386852118945</v>
+        <v>-4.354305419197559</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.065360148924775</v>
       </c>
       <c r="E98">
-        <v>-41.64213955230631</v>
+        <v>-42.85995036787105</v>
       </c>
       <c r="F98">
-        <v>-2.915819442038253</v>
+        <v>-2.004466192826293</v>
       </c>
       <c r="G98">
-        <v>-4.68166871484839</v>
+        <v>-4.762955850019654</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.516129288556362</v>
       </c>
       <c r="E99">
-        <v>-44.3227244564067</v>
+        <v>-44.91169778584431</v>
       </c>
       <c r="F99">
-        <v>-3.558534799257139</v>
+        <v>-2.495656584725093</v>
       </c>
       <c r="G99">
-        <v>-5.141053256059817</v>
+        <v>-4.952107179951454</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.992169246162794</v>
       </c>
       <c r="E100">
-        <v>-46.78437349189526</v>
+        <v>-47.63014299688583</v>
       </c>
       <c r="F100">
-        <v>-3.659315634216532</v>
+        <v>-2.720862345421986</v>
       </c>
       <c r="G100">
-        <v>-5.585613174346387</v>
+        <v>-4.886372987723685</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.44980756225899</v>
       </c>
       <c r="E101">
-        <v>-49.53915631049283</v>
+        <v>-49.63852801199864</v>
       </c>
       <c r="F101">
-        <v>-4.105944830049136</v>
+        <v>-3.091492973884749</v>
       </c>
       <c r="G101">
-        <v>-5.340026974606633</v>
+        <v>-5.366107452365012</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.93386188935438</v>
       </c>
       <c r="E102">
-        <v>-51.15164401395907</v>
+        <v>-52.84650013115083</v>
       </c>
       <c r="F102">
-        <v>-4.439442232946606</v>
+        <v>-3.696830737154516</v>
       </c>
       <c r="G102">
-        <v>-5.535104181053727</v>
+        <v>-5.870753772189354</v>
       </c>
     </row>
   </sheetData>
